--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136006185</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136006181</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136006184</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136006186</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136006185</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136006181</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136006184</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136006186</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136006185</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136006181</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136006184</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136006186</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>136006185</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136006181</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136006184</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>136006186</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
